--- a/文本分析/BERTopic/千秋梦/InteractiveSheet_2026-04-07_千秋梦.xlsx
+++ b/文本分析/BERTopic/千秋梦/InteractiveSheet_2026-04-07_千秋梦.xlsx
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+  <si>
+    <t>Topic</t>
+  </si>
   <si>
     <t>Count</t>
   </si>
@@ -1317,19 +1320,28 @@
   </sheetPr>
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="12.6272727272727" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="5.81818181818182" customWidth="1"/>
+    <col min="2" max="2" width="6.27272727272727" customWidth="1"/>
+    <col min="3" max="3" width="25.8181818181818" customWidth="1"/>
+    <col min="4" max="4" width="46.7272727272727" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:5">
@@ -1340,13 +1352,13 @@
         <v>3934</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:5">
@@ -1357,13 +1369,13 @@
         <v>2490</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:5">
@@ -1374,13 +1386,13 @@
         <v>1143</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:5">
@@ -1391,13 +1403,13 @@
         <v>808</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:5">
@@ -1408,13 +1420,13 @@
         <v>439</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:5">
@@ -1425,13 +1437,13 @@
         <v>399</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:5">
@@ -1442,13 +1454,13 @@
         <v>296</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:5">
@@ -1459,13 +1471,13 @@
         <v>99</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:5">
@@ -1476,13 +1488,13 @@
         <v>84</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:5">
@@ -1493,13 +1505,13 @@
         <v>76</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:5">
@@ -1510,13 +1522,13 @@
         <v>67</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:5">
@@ -1527,13 +1539,13 @@
         <v>65</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:5">
@@ -1544,13 +1556,13 @@
         <v>56</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:5">
@@ -1561,13 +1573,13 @@
         <v>55</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:5">
@@ -1578,13 +1590,13 @@
         <v>54</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:5">
@@ -1595,13 +1607,13 @@
         <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:5">
@@ -1612,13 +1624,13 @@
         <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:5">
@@ -1629,13 +1641,13 @@
         <v>44</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:5">
@@ -1646,13 +1658,13 @@
         <v>41</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
